--- a/docs/revised_shatin/qwen3-235b-a22b-thinking-2507/test_grammar_3_['No. 23_～たら〈条件(じょうけん)〉 ']_revised_iteration_4.xlsx
+++ b/docs/revised_shatin/qwen3-235b-a22b-thinking-2507/test_grammar_3_['No. 23_～たら〈条件(じょうけん)〉 ']_revised_iteration_4.xlsx
@@ -467,12 +467,12 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい1 映画の始まる30分前なら、(   )。</t>
+          <t>: もんだい1 もし時間があったら、(   )。</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>1. トイレに行きます 2. 買い物をします 3. 散歩に行きます 4. 料理をします</t>
+          <t>1. 映画を見ます 2. 買い物をします 3. 散歩に行きます 4. 料理をします</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr">
@@ -491,7 +491,7 @@
       </c>
       <c r="B3" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい1 長い試験が終わったら、すぐに(   )。</t>
+          <t>: もんだい1 しけんが終わったら、(   )。</t>
         </is>
       </c>
       <c r="C3" s="1" t="inlineStr">
@@ -501,7 +501,7 @@
       </c>
       <c r="D3" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E3" s="1" t="inlineStr"/>
@@ -515,12 +515,12 @@
       </c>
       <c r="B4" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい1 家に帰って、とても疲れました。まず(   )。</t>
+          <t>: もんだい1 家に帰ったら、すぐに(   )。</t>
         </is>
       </c>
       <c r="C4" s="1" t="inlineStr">
         <is>
-          <t>1. 休みます 2. テレビを見ます 3. 夕食を作ります 4. 勉強します</t>
+          <t>1. 休みました 2. テレビを見ました 3. 夕食を作りました 4. 勉強しました</t>
         </is>
       </c>
       <c r="D4" s="1" t="inlineStr">
@@ -539,7 +539,7 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい1 本を読んだら、感想を日記に(   )。</t>
+          <t>: もんだい1 本を読んだら、感想を（   ）。</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
@@ -563,20 +563,17 @@
       </c>
       <c r="B6" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 旅行が終わったら、お土産を家族に(   )。</t>
+          <t>: もんだい1 旅行が終わったら、（   ）。</t>
         </is>
       </c>
       <c r="C6" s="1" t="inlineStr">
         <is>
-          <t>1. ほめます
-2. 渡します
-3. 教えます
-4. かります</t>
+          <t>1. 写真を整理します 2. お土産を食べます 3. 旅程を変更します 4. 予約をキャンセルします</t>
         </is>
       </c>
       <c r="D6" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E6" s="1" t="inlineStr"/>
@@ -590,17 +587,17 @@
       </c>
       <c r="B7" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい1 朝起きたら、(   )。</t>
+          <t>: もんだい1 朝ごはんを食べたら、（   ）。</t>
         </is>
       </c>
       <c r="C7" s="1" t="inlineStr">
         <is>
-          <t>1. 仕事に行きます 2. 新聞を読みます 3. 歯を磨きます 4. 服を着替えます</t>
+          <t>1. 会社へ行きます 2. 寝ます 3. 夕食の準備をします 4. お風呂に入ります</t>
         </is>
       </c>
       <c r="D7" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E7" s="1" t="inlineStr"/>
@@ -614,12 +611,12 @@
       </c>
       <c r="B8" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい1 電話が来たら、(   )。</t>
+          <t>: もんだい1 電話が来たら、出たほうが（ ）。</t>
         </is>
       </c>
       <c r="C8" s="1" t="inlineStr">
         <is>
-          <t>1. 出ます 2. 切ります 3. メッセージを送ります 4. 電話を無視します</t>
+          <t>1. いい 2. ため 3. こと 4. つもり</t>
         </is>
       </c>
       <c r="D8" s="1" t="inlineStr">
@@ -638,20 +635,17 @@
       </c>
       <c r="B9" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 日本に来たら、富士山を(   )。</t>
+          <t>: もんだい1 雨が降ったら、傘をさすのが一番(   )ことです。</t>
         </is>
       </c>
       <c r="C9" s="1" t="inlineStr">
         <is>
-          <t>1. 買います
-2. 見ます
-3. 作ります
-4. たべます</t>
+          <t>1. いい 2. よく 3. よかった 4. よくて</t>
         </is>
       </c>
       <c r="D9" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E9" s="1" t="inlineStr"/>
@@ -665,12 +659,12 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい1 お金があったら、新しいカメラを(   )。</t>
+          <t>: もんだい1 お金があったら、（   ）。</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>1. 買います 2. 修理します 3. 掃除します 4. 行きます</t>
+          <t>1. 旅行に行きます 2. 薬を飲みます 3. 傘を買います 4. ごみを出します</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr">
@@ -689,7 +683,7 @@
       </c>
       <c r="B11" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい2 雨が ふったら サッカーの試合は 中止 (   ) なる。</t>
+          <t>: もんだい2 雨が降ったら、サッカーの試合は中止（ ）なります。</t>
         </is>
       </c>
       <c r="C11" s="1" t="inlineStr">
@@ -708,12 +702,12 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Q11</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい2 このボタンを 押したら、ドアが (   )。</t>
+          <t>: もんだい2 このボタンを 押したら、ドアが (   )。</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
@@ -732,12 +726,12 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>Q12</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="B13" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい2 友だちが 来たら いっしょ (   ) 食事を しましょう。</t>
+          <t>: もんだい2 友だちが 来たら いっしょ (   ) 食事を しましょう。</t>
         </is>
       </c>
       <c r="C13" s="1" t="inlineStr">
@@ -756,17 +750,17 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Q13</t>
+          <t>Q3</t>
         </is>
       </c>
       <c r="B14" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい2 かぜを ひいたら、早く 寝る (   ) いいですよ。</t>
+          <t>: もんだい2 かぜをひいたら、早く寝た（   ）がいいですよ。</t>
         </is>
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>1. ほう 2. ため 3. こと 4. つもり</t>
+          <t>1. ほう 2. ため 3. もの 4. こと</t>
         </is>
       </c>
       <c r="D14" s="1" t="inlineStr">
@@ -780,12 +774,12 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>Q14</t>
+          <t>Q4</t>
         </is>
       </c>
       <c r="B15" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい2 お金を ためたら、新しい パソコン (   ) 買うつもりです。</t>
+          <t>: もんだい2 お金を ためたら、新しい パソコン (   ) 買うつもりです。</t>
         </is>
       </c>
       <c r="C15" s="1" t="inlineStr">
@@ -804,12 +798,12 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Q15</t>
+          <t>Q5</t>
         </is>
       </c>
       <c r="B16" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい2 駅に 着いたら 電話 (   ) ください。</t>
+          <t>: もんだい2 駅に 着いたら 電話 (   ) ください。</t>
         </is>
       </c>
       <c r="C16" s="1" t="inlineStr">
@@ -828,12 +822,12 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>Q16</t>
+          <t>Q6</t>
         </is>
       </c>
       <c r="B17" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい2 もし、彼に 会えたら、この 手紙を (   )。</t>
+          <t>: もんだい2 もし、彼に 会えたら、この 手紙を (   )。</t>
         </is>
       </c>
       <c r="C17" s="1" t="inlineStr">
@@ -852,12 +846,12 @@
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>Q17</t>
+          <t>Q7</t>
         </is>
       </c>
       <c r="B18" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい2 宿題が 終わったら、遊びに (   ) 行きましょう。</t>
+          <t>: もんだい2 宿題が 終わったら、遊びに (   ) 行きましょう。</t>
         </is>
       </c>
       <c r="C18" s="1" t="inlineStr">
@@ -876,12 +870,12 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>Q18</t>
+          <t>Q8</t>
         </is>
       </c>
       <c r="B19" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい2 天気が よかったら、明日 (   ) 行きます。</t>
+          <t>: もんだい2 天気が よかったら、明日 (   ) 行きます。</t>
         </is>
       </c>
       <c r="C19" s="1" t="inlineStr">
@@ -900,12 +894,12 @@
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>Q19</t>
+          <t>Q9</t>
         </is>
       </c>
       <c r="B20" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい2 時間が あったら、映画を (   ) 見に行きます。</t>
+          <t>: もんだい2 時間が あったら、映画を (   ) 見に行きます。</t>
         </is>
       </c>
       <c r="C20" s="1" t="inlineStr">
@@ -924,12 +918,12 @@
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>Q20</t>
+          <t>Q10</t>
         </is>
       </c>
       <c r="B21" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい3 雨が降ったら、(   )。</t>
+          <t>: もんだい3 雨が降ったら、(   )。</t>
         </is>
       </c>
       <c r="C21" s="1" t="inlineStr">
@@ -948,12 +942,12 @@
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>Q21</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="B22" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい3 宿題が終わったら、(   )。</t>
+          <t>: もんだい3 宿題が終わったら、(   )。</t>
         </is>
       </c>
       <c r="C22" s="1" t="inlineStr">
@@ -972,12 +966,12 @@
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>Q22</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="B23" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい3 お金を持っていたら、(   )。</t>
+          <t>: もんだい3 お金を持っていたら、(   )。</t>
         </is>
       </c>
       <c r="C23" s="1" t="inlineStr">
@@ -996,12 +990,12 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>Q23</t>
+          <t>Q3</t>
         </is>
       </c>
       <c r="B24" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい3 時間があったら、(   )。</t>
+          <t>: もんだい3 時間があったら、(   )。</t>
         </is>
       </c>
       <c r="C24" s="1" t="inlineStr">
@@ -1020,17 +1014,17 @@
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>Q24</t>
+          <t>Q4</t>
         </is>
       </c>
       <c r="B25" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい3 図書館に行ったら、(   )。</t>
+          <t>: もんだい3 図書館に行ったら、最初に必ず（ ）。</t>
         </is>
       </c>
       <c r="C25" s="1" t="inlineStr">
         <is>
-          <t>1. 本を借ります 2. 本を読む 3. 本を探す 4. 本を返す</t>
+          <t>1. 本を借ります 2. 静かにします 3. 飲み物を買います 4. 電話をします</t>
         </is>
       </c>
       <c r="D25" s="1" t="inlineStr">
@@ -1044,17 +1038,17 @@
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>Q25</t>
+          <t>Q5</t>
         </is>
       </c>
       <c r="B26" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい3 友達が来たら、(   )。</t>
+          <t>: もんだい3 友達が急に来たら、普通は（   ）。</t>
         </is>
       </c>
       <c r="C26" s="1" t="inlineStr">
         <is>
-          <t>1. パーティーをします 2. 話をします 3. 一緒に遊びます 4. お茶を飲みます</t>
+          <t>1. お茶を出します 2. 大掃除をします 3. 電話をかけます 4. お金を請求します</t>
         </is>
       </c>
       <c r="D26" s="1" t="inlineStr">
@@ -1068,12 +1062,12 @@
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>Q26</t>
+          <t>Q6</t>
         </is>
       </c>
       <c r="B27" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい3 電車が遅れたら、(   )。</t>
+          <t>: もんだい3 電車が遅れたら、(   )。</t>
         </is>
       </c>
       <c r="C27" s="1" t="inlineStr">
@@ -1092,12 +1086,12 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>Q27</t>
+          <t>Q7</t>
         </is>
       </c>
       <c r="B28" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい3 映画が終わったら、(   )。</t>
+          <t>: もんだい3 映画が終わったら、(   )。</t>
         </is>
       </c>
       <c r="C28" s="1" t="inlineStr">
@@ -1116,17 +1110,17 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>Q28</t>
+          <t>Q8</t>
         </is>
       </c>
       <c r="B29" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい3 もし雨が降ったら、(   )。</t>
+          <t>: もんだい3 もし雨が降ったら、（   ）。</t>
         </is>
       </c>
       <c r="C29" s="1" t="inlineStr">
         <is>
-          <t>1. 傘をさします 2. 雨宿りします 3. 帰ります 4. 走ります</t>
+          <t>1. 傘をさします 2. サングラスをかけます 3. ビーチに行きます 4. 扇風機を使います</t>
         </is>
       </c>
       <c r="D29" s="1" t="inlineStr">
@@ -1140,17 +1134,17 @@
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>Q29</t>
+          <t>Q9</t>
         </is>
       </c>
       <c r="B30" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい3 冬になったら、(   )。</t>
+          <t>: もんだい3 冬になったら、（   ）。</t>
         </is>
       </c>
       <c r="C30" s="1" t="inlineStr">
         <is>
-          <t>1. さむくなります 2. コートを着ます 3. スキーをします 4. 暖房を使います</t>
+          <t>1. さむくなります 2. サイクリングをします 3. プールに行きます 4. アイスクリームを食べます</t>
         </is>
       </c>
       <c r="D30" s="1" t="inlineStr">
@@ -1164,12 +1158,12 @@
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>Q30</t>
+          <t>Q10</t>
         </is>
       </c>
       <c r="B31" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい4 もし お金が たくさん あったら、 新しい車を (   ).</t>
+          <t>: もんだい4 もし お金が たくさん あったら、 新しい車を (   ).</t>
         </is>
       </c>
       <c r="C31" s="1" t="inlineStr">
@@ -1188,12 +1182,12 @@
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>Q31</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="B32" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい4 もし 雨が 降ったら、 試合は (   ).</t>
+          <t>: もんだい4 もし 雨が 降ったら、 試合は (   ).</t>
         </is>
       </c>
       <c r="C32" s="1" t="inlineStr">
@@ -1212,12 +1206,12 @@
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>Q32</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="B33" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい4 試験が 終わったら、 わたしは 映画を 見に行く (   ).</t>
+          <t>: もんだい4 試験が 終わったら、 わたしは 映画を 見に行く (   ).</t>
         </is>
       </c>
       <c r="C33" s="1" t="inlineStr">
@@ -1236,12 +1230,12 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>Q33</t>
+          <t>Q3</t>
         </is>
       </c>
       <c r="B34" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい4 もし 暇だったら、 手伝いに (   ).</t>
+          <t>: もんだい4 もし 暇だったら、 手伝いに (   ).</t>
         </is>
       </c>
       <c r="C34" s="1" t="inlineStr">
@@ -1260,12 +1254,12 @@
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>Q34</t>
+          <t>Q4</t>
         </is>
       </c>
       <c r="B35" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい4 もし 時間が あったら、 新しいレストランで 食事を (   ).</t>
+          <t>: もんだい4 もし 時間が あったら、 新しいレストランで 食事を (   ).</t>
         </is>
       </c>
       <c r="C35" s="1" t="inlineStr">
@@ -1284,17 +1278,17 @@
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>Q35</t>
+          <t>Q5</t>
         </is>
       </c>
       <c r="B36" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい4 仕事が 終わったら、 友だちと カフェに (   ).</t>
+          <t>: もんだい4 仕事が 終わったら、 友だちと カフェに (   ).</t>
         </is>
       </c>
       <c r="C36" s="1" t="inlineStr">
         <is>
-          <t>1. 行くことにした 2. 行きたい 3. 行くかもしれない 4. 行った</t>
+          <t>1. 行くことにしました 2. 行きたいです 3. 行くかもしれません 4. 行きました</t>
         </is>
       </c>
       <c r="D36" s="1" t="inlineStr">
@@ -1308,12 +1302,12 @@
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>Q36</t>
+          <t>Q6</t>
         </is>
       </c>
       <c r="B37" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい4 もし 試験に 合格したら、 旅行に (   ).</t>
+          <t>: もんだい4 もし 試験に 合格したら、 旅行に (   ).</t>
         </is>
       </c>
       <c r="C37" s="1" t="inlineStr">
@@ -1332,12 +1326,12 @@
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>Q37</t>
+          <t>Q7</t>
         </is>
       </c>
       <c r="B38" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい4 もし 彼が 来たら、 お祝いを (   ).</t>
+          <t>: もんだい4 もし 彼が 来たら、 お祝いを (   ).</t>
         </is>
       </c>
       <c r="C38" s="1" t="inlineStr">
@@ -1356,12 +1350,12 @@
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>Q38</t>
+          <t>Q8</t>
         </is>
       </c>
       <c r="B39" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい4 もし 間違えたら、 すぐに 先生に (   ).</t>
+          <t>: もんだい4 もし 間違えたら、 すぐに 先生に (   ).</t>
         </is>
       </c>
       <c r="C39" s="1" t="inlineStr">
@@ -1380,12 +1374,12 @@
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>Q39</t>
+          <t>Q9</t>
         </is>
       </c>
       <c r="B40" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい4 もし 彼女が 行かないなら、 わたしも 行かない (   ).</t>
+          <t>: もんだい4 もし 彼女が 行かないなら、 わたしも 行かない (   ).</t>
         </is>
       </c>
       <c r="C40" s="1" t="inlineStr">
@@ -1404,12 +1398,12 @@
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>Q40</t>
+          <t>Q10</t>
         </is>
       </c>
       <c r="B41" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい5 雨が降ったら、試合は (   )。</t>
+          <t>: もんだい5 雨が降ったら、試合は (   )。</t>
         </is>
       </c>
       <c r="C41" s="1" t="inlineStr">
@@ -1428,12 +1422,12 @@
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>Q41</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="B42" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい5 もし彼が来たら、私はすぐに (   )。</t>
+          <t>: もんだい5 もし彼が来たら、私はすぐに (   )。</t>
         </is>
       </c>
       <c r="C42" s="1" t="inlineStr">
@@ -1452,12 +1446,12 @@
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>Q42</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="B43" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい5 この仕事が終わったら、(   )。</t>
+          <t>: もんだい5 この仕事が終わったら、(   )。</t>
         </is>
       </c>
       <c r="C43" s="1" t="inlineStr">
@@ -1476,12 +1470,12 @@
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>Q43</t>
+          <t>Q3</t>
         </is>
       </c>
       <c r="B44" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい5 時間があったら、映画を (   )。</t>
+          <t>: もんだい5 時間があったら、映画を (   )。</t>
         </is>
       </c>
       <c r="C44" s="1" t="inlineStr">
@@ -1500,12 +1494,12 @@
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>Q44</t>
+          <t>Q4</t>
         </is>
       </c>
       <c r="B45" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい5 彼女が手伝ったら、もっと早く (   )。</t>
+          <t>: もんだい5 彼女が手伝ったら、もっと早く (   )。</t>
         </is>
       </c>
       <c r="C45" s="1" t="inlineStr">
@@ -1524,17 +1518,17 @@
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>Q45</t>
+          <t>Q5</t>
         </is>
       </c>
       <c r="B46" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい5 この本を読んだら、次に何を (   )。</t>
+          <t>: もんだい5 この本を読んだら、次に何を（   ）。</t>
         </is>
       </c>
       <c r="C46" s="1" t="inlineStr">
         <is>
-          <t>1. 読みますか 2. 書きますか 3. 聞きますか 4. 見ますか</t>
+          <t>1. 読みますか 2. 調べますか 3. 焼きますか 4. 洗いますか</t>
         </is>
       </c>
       <c r="D46" s="1" t="inlineStr">
@@ -1548,12 +1542,12 @@
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>Q46</t>
+          <t>Q6</t>
         </is>
       </c>
       <c r="B47" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい5 友達が来たら、ゲームを一緒に (   )。</t>
+          <t>: もんだい5 友達が来たら、ゲームを一緒に (   )。</t>
         </is>
       </c>
       <c r="C47" s="1" t="inlineStr">
@@ -1572,12 +1566,12 @@
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>Q47</t>
+          <t>Q7</t>
         </is>
       </c>
       <c r="B48" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい5 電車が遅れたら、授業に (   )。</t>
+          <t>: もんだい5 電車が遅れたら、授業に (   )。</t>
         </is>
       </c>
       <c r="C48" s="1" t="inlineStr">
@@ -1596,12 +1590,12 @@
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>Q48</t>
+          <t>Q8</t>
         </is>
       </c>
       <c r="B49" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい5 もしお金がたくさんあったら、旅行に (   )。</t>
+          <t>: もんだい5 もしお金がたくさんあったら、旅行に（   ）。</t>
         </is>
       </c>
       <c r="C49" s="1" t="inlineStr">
@@ -1620,17 +1614,17 @@
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>Q49</t>
+          <t>Q9</t>
         </is>
       </c>
       <c r="B50" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい5 彼が答えたら、みんなが (   )。</t>
+          <t>: もんだい5 彼が悲しい答えを言ったら、みんなが（   ）。</t>
         </is>
       </c>
       <c r="C50" s="1" t="inlineStr">
         <is>
-          <t>1. 驚きます 2. 怒ります 3. 笑います 4. 泣きます</t>
+          <t>1. 泣きます 2. 笑います 3. 走ります 4. 遊びます</t>
         </is>
       </c>
       <c r="D50" s="1" t="inlineStr">
@@ -1644,12 +1638,12 @@
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>Q50</t>
+          <t>Q10</t>
         </is>
       </c>
       <c r="B51" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい6 A:「雨が降ったら、どうしますか。 」 B:「雨が降ったら、家で映画を(   )。 」</t>
+          <t>: もんだい6 A:「雨が降ったら、どうしますか。 」 B:「雨が降ったら、家で映画を(   )。 」</t>
         </is>
       </c>
       <c r="C51" s="1" t="inlineStr">
@@ -1668,12 +1662,12 @@
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>Q51</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="B52" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい6 A:「もし道に迷ったら、どうしますか。 」 B:「すぐにアプリで(   )。 」</t>
+          <t>: もんだい6 A:「もし道に迷ったら、どうしますか。 」 B:「すぐにアプリで(   )。 」</t>
         </is>
       </c>
       <c r="C52" s="1" t="inlineStr">
@@ -1692,12 +1686,12 @@
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>Q52</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="B53" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい6 A:「テストが終わったら、何をしますか。 」 B:「終わったら、友達とカフェに(   )。 」</t>
+          <t>: もんだい6 A:「テストが終わったら、何をしますか。 」 B:「終わったら、友達とカフェに(   )。 」</t>
         </is>
       </c>
       <c r="C53" s="1" t="inlineStr">
@@ -1716,12 +1710,12 @@
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>Q53</t>
+          <t>Q3</t>
         </is>
       </c>
       <c r="B54" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい6 A:「明日暇(ひま)だったら、何をしますか。 」 B:「暇だったら、家でゆっくり(   )。 」</t>
+          <t>: もんだい6 A:「明日暇(ひま)だったら、何をしますか。 」 B:「暇だったら、家でゆっくり(   )。 」</t>
         </is>
       </c>
       <c r="C54" s="1" t="inlineStr">
@@ -1740,12 +1734,12 @@
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>Q54</t>
+          <t>Q4</t>
         </is>
       </c>
       <c r="B55" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい6 A:「もし、時間があったら、手伝ってもらえますか。 」 B:「時間があったら、もちろん(   )。 」</t>
+          <t>: もんだい6 A:「もし、時間があったら、手伝ってもらえますか。 」 B:「時間があったら、もちろん(   )。 」</t>
         </is>
       </c>
       <c r="C55" s="1" t="inlineStr">
@@ -1764,12 +1758,12 @@
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>Q55</t>
+          <t>Q5</t>
         </is>
       </c>
       <c r="B56" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい6 A:「もし、今週末に予定がなかったら、どこに行きたいですか。 」 B:「予定がなかったら、海に(   )。 」</t>
+          <t>: もんだい6 A:「もし、今週末に予定がなかったら、どこに行きたいですか。 」 B:「予定がなかったら、海に(   )。 」</t>
         </is>
       </c>
       <c r="C56" s="1" t="inlineStr">
@@ -1788,12 +1782,12 @@
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>Q56</t>
+          <t>Q6</t>
         </is>
       </c>
       <c r="B57" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい6 A:「バスが遅れたら、どうしますか。 」 B:「遅れたら、タクシーを(   )。 」</t>
+          <t>: もんだい6 A:「バスが遅れたら、どうしますか。 」 B:「遅れたら、タクシーを(   )。 」</t>
         </is>
       </c>
       <c r="C57" s="1" t="inlineStr">
@@ -1812,12 +1806,12 @@
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>Q57</t>
+          <t>Q7</t>
         </is>
       </c>
       <c r="B58" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい6 A:「もし、財布を忘れたら、どうしますか。 」 B:「忘れたら、友達に(   )。 」</t>
+          <t>: もんだい6 A:「もし、財布を忘れたら、どうしますか。 」 B:「忘れたら、友達に(   )。 」</t>
         </is>
       </c>
       <c r="C58" s="1" t="inlineStr">
@@ -1836,12 +1830,12 @@
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>Q58</t>
+          <t>Q8</t>
         </is>
       </c>
       <c r="B59" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい6 A:「もし、雨が降ったら、ピクニックはどうしますか。 」 B:「雨が降ったら、ピクニックは(   )。 」</t>
+          <t>: もんだい6 A:「もし、雨が降ったら、ピクニックはどうしますか。 」 B:「雨が降ったら、ピクニックは(   )。 」</t>
         </is>
       </c>
       <c r="C59" s="1" t="inlineStr">
@@ -1860,12 +1854,12 @@
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>Q59</t>
+          <t>Q9</t>
         </is>
       </c>
       <c r="B60" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい6 A:「試験に合格したら、何をしますか。 」 B:「合格したら、家族と(   )。 」</t>
+          <t>: もんだい6 A:「試験に合格したら、何をしますか。 」 B:「合格したら、家族と(   )。 」</t>
         </is>
       </c>
       <c r="C60" s="1" t="inlineStr">
@@ -1884,22 +1878,22 @@
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>Q60</t>
+          <t>Q10</t>
         </is>
       </c>
       <c r="B61" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい7 もし 雨が 降ったら (   )。</t>
+          <t>: もんだい7 もし雨が降ったら、（   ）。</t>
         </is>
       </c>
       <c r="C61" s="1" t="inlineStr">
         <is>
-          <t>1. 行ける 2. 行けない 3. 行こう 4. 行く</t>
+          <t>1. 傘をさします 2. 日焼けします 3. 水遊びをします 4. テニスを続けます</t>
         </is>
       </c>
       <c r="D61" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E61" s="1" t="inlineStr"/>
@@ -1908,12 +1902,12 @@
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>Q61</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="B62" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい7 テストが 終わったら (   )。</t>
+          <t>: もんだい7 テストが 終わったら (   )。</t>
         </is>
       </c>
       <c r="C62" s="1" t="inlineStr">
@@ -1932,12 +1926,12 @@
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>Q62</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="B63" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい7 もし お金が あったら、(   )。</t>
+          <t>: もんだい7 もし お金が あったら、(   )。</t>
         </is>
       </c>
       <c r="C63" s="1" t="inlineStr">
@@ -1956,12 +1950,12 @@
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>Q63</t>
+          <t>Q3</t>
         </is>
       </c>
       <c r="B64" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい7 時間が あったら (   )。</t>
+          <t>: もんだい7 時間が あったら (   )。</t>
         </is>
       </c>
       <c r="C64" s="1" t="inlineStr">
@@ -1980,12 +1974,12 @@
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>Q64</t>
+          <t>Q4</t>
         </is>
       </c>
       <c r="B65" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい7 もし 彼が 来たら、(   )。</t>
+          <t>: もんだい7 もし 彼が 来たら、(   )。</t>
         </is>
       </c>
       <c r="C65" s="1" t="inlineStr">
@@ -2004,12 +1998,12 @@
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>Q65</t>
+          <t>Q5</t>
         </is>
       </c>
       <c r="B66" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい7 パーティーが 終わったら (   )。</t>
+          <t>: もんだい7 パーティーが 終わったら (   )。</t>
         </is>
       </c>
       <c r="C66" s="1" t="inlineStr">
@@ -2028,12 +2022,12 @@
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>Q66</t>
+          <t>Q6</t>
         </is>
       </c>
       <c r="B67" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい7 彼女が 行くと 言ったら、(   )。</t>
+          <t>: もんだい7 彼女が 行くと 言ったら、(   )。</t>
         </is>
       </c>
       <c r="C67" s="1" t="inlineStr">
@@ -2052,12 +2046,12 @@
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>Q67</t>
+          <t>Q7</t>
         </is>
       </c>
       <c r="B68" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい7 もし 道が わからなかったら、(   )。</t>
+          <t>: もんだい7 もし 道が わからなかったら、(   )。</t>
         </is>
       </c>
       <c r="C68" s="1" t="inlineStr">
@@ -2076,12 +2070,12 @@
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>Q68</t>
+          <t>Q8</t>
         </is>
       </c>
       <c r="B69" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい7 天気が よかったら、(   )。</t>
+          <t>: もんだい7 天気が よかったら、(   )。</t>
         </is>
       </c>
       <c r="C69" s="1" t="inlineStr">
@@ -2100,12 +2094,12 @@
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>Q69</t>
+          <t>Q9</t>
         </is>
       </c>
       <c r="B70" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい7 先生が 来たら、(   )。</t>
+          <t>: もんだい7 先生が 来たら、(   )。</t>
         </is>
       </c>
       <c r="C70" s="1" t="inlineStr">
@@ -2124,12 +2118,12 @@
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>Q70</t>
+          <t>Q10</t>
         </is>
       </c>
       <c r="B71" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい8 雨が降ったら、試合は(   )中止(ちゅうし)になります。</t>
+          <t>: もんだい8 雨が降ったら、試合は(   )中止(ちゅうし)になります。</t>
         </is>
       </c>
       <c r="C71" s="1" t="inlineStr">
@@ -2148,17 +2142,17 @@
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>Q71</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="B72" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい8 このケーキを食べたら、まるで天国(てんごく)にいる(   )美味(おい)しさです。</t>
+          <t>: もんだい8 このケーキを食べたら、まるで（   ）にいるようでした。</t>
         </is>
       </c>
       <c r="C72" s="1" t="inlineStr">
         <is>
-          <t>1. ような 2. らしい 3. ほど 4. みたいな</t>
+          <t>1. 夢の世界 2. 天使の羽 3. 魔法の杖 4. 音楽の海</t>
         </is>
       </c>
       <c r="D72" s="1" t="inlineStr">
@@ -2172,12 +2166,12 @@
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>Q72</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="B73" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい8 彼女(かのじょ)が来たら、部屋(へや)が明るくなった(   )感じ(かんじ)です。</t>
+          <t>: もんだい8 彼女が来たら、部屋が明るくなった（   ）感じです。</t>
         </is>
       </c>
       <c r="C73" s="1" t="inlineStr">
@@ -2196,17 +2190,17 @@
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>Q73</t>
+          <t>Q3</t>
         </is>
       </c>
       <c r="B74" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい8 食事(しょくじ)が終わったら、(   )映画(えいが)を見に行きましょう。</t>
+          <t>: もんだい8 食事(しょくじ)が終わったら、（ ）映画(えいが)を見に行きましょう。</t>
         </is>
       </c>
       <c r="C74" s="1" t="inlineStr">
         <is>
-          <t>1. ように 2. ほどに 3. みたいに 4. らしく</t>
+          <t>1. さっそく 2. ほどに 3. みたいに 4. らしく</t>
         </is>
       </c>
       <c r="D74" s="1" t="inlineStr">
@@ -2220,12 +2214,12 @@
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>Q74</t>
+          <t>Q4</t>
         </is>
       </c>
       <c r="B75" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい8 彼(かれ)の話(はなし)を聞いたら、夢(ゆめ)を見ている(   )気分(きぶん)になりました。</t>
+          <t>: もんだい8 彼(かれ)の話(はなし)を聞いたら、夢(ゆめ)を見ている(   )気分(きぶん)になりました。</t>
         </is>
       </c>
       <c r="C75" s="1" t="inlineStr">
@@ -2244,12 +2238,12 @@
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>Q75</t>
+          <t>Q5</t>
         </is>
       </c>
       <c r="B76" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい8 お金(かね)があったら、まるで王様(おうさま)の(   )生活(せいかつ)ができるでしょう。</t>
+          <t>: もんだい8 お金(かね)があったら、まるで王様(おうさま)の(   )生活(せいかつ)ができるでしょう。</t>
         </is>
       </c>
       <c r="C76" s="1" t="inlineStr">
@@ -2268,12 +2262,12 @@
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>Q76</t>
+          <t>Q6</t>
         </is>
       </c>
       <c r="B77" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい8 宿題(しゅくだい)が終わったら、(   )遊(あそ)びに行けます。</t>
+          <t>: もんだい8 宿題(しゅくだい)が終わったら、(   )遊(あそ)びに行けます。</t>
         </is>
       </c>
       <c r="C77" s="1" t="inlineStr">
@@ -2292,22 +2286,22 @@
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>Q77</t>
+          <t>Q7</t>
         </is>
       </c>
       <c r="B78" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい8 彼(かれ)は試験(しけん)に合格(ごうかく)したら、(   )喜(よろこ)びました。</t>
+          <t>: もんだい8 彼は試験に合格したら、（   ）喜びました。</t>
         </is>
       </c>
       <c r="C78" s="1" t="inlineStr">
         <is>
-          <t>1. みたいに 2. ように 3. ほどに 4. らしく</t>
+          <t>1. すごいほどに 2. とても 3. みたいに 4. らしく</t>
         </is>
       </c>
       <c r="D78" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E78" s="1" t="inlineStr"/>
@@ -2316,17 +2310,17 @@
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>Q78</t>
+          <t>Q8</t>
         </is>
       </c>
       <c r="B79" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい8 もし雨(あめ)が降ったら、(   )家(いえ)に帰(かえ)ります。</t>
+          <t>: もんだい8 もし雨(あめ)が降ったら、（ ）家(いえ)に帰(かえ)ります。</t>
         </is>
       </c>
       <c r="C79" s="1" t="inlineStr">
         <is>
-          <t>1. ほどに 2. ように 3. みたいに 4. らしく</t>
+          <t>1. まもなく 2. すぐに 3. みたいに 4. らしく</t>
         </is>
       </c>
       <c r="D79" s="1" t="inlineStr">
@@ -2340,12 +2334,12 @@
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>Q79</t>
+          <t>Q9</t>
         </is>
       </c>
       <c r="B80" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい8 彼女(かのじょ)が笑(わら)ったら、太陽(たいよう)が輝(かがや)く(   )明(あか)るいです。</t>
+          <t>: もんだい8 彼女(かのじょ)が笑(わら)ったら、太陽(たいよう)が輝(かがや)く(   )明(あか)るいです。</t>
         </is>
       </c>
       <c r="C80" s="1" t="inlineStr">
